--- a/tables_and_figures/input_tables/vars_used_by_anesrake.xlsx
+++ b/tables_and_figures/input_tables/vars_used_by_anesrake.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not provided</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
